--- a/dados/excel/secretaria_cargo.xlsx
+++ b/dados/excel/secretaria_cargo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -914,10 +914,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>94934.22</v>
+        <v>94934.17</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>5584.37</v>
+        <v>5584.36</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>5629.07</v>
@@ -988,23 +988,23 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>INAT/PENS(OF.MANUT/CONSERVAC)</t>
+          <t>INAT/PENS(OF.CALCETEIRO)</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
         <v>7</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>32442.6</v>
+        <v>25708.86</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>4634.66</v>
+        <v>3672.69</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>4999.17</v>
+        <v>3689.19</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1015,23 +1015,23 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>INAT/PENS(OF.CALCETEIRO)</t>
+          <t>INAT/PENS(OF.MANUT/CONSERVAC)</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>25708.89</v>
+        <v>27283.44</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3672.7</v>
+        <v>4547.24</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3689.2</v>
+        <v>4522.11</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="9">
@@ -1049,13 +1049,13 @@
         <v>6</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>43832.32</v>
+        <v>43832.24</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>7305.39</v>
+        <v>7305.37</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>7618.78</v>
+        <v>7618.76</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>50</v>
@@ -1076,13 +1076,13 @@
         <v>54</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>506631.57</v>
+        <v>507809.09</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>9382.07</v>
+        <v>9403.870000000001</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7507.05</v>
+        <v>8104.1</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>92.59</v>
@@ -1103,13 +1103,13 @@
         <v>35</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>310425.91</v>
+        <v>299039.44</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>8869.309999999999</v>
+        <v>8543.98</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>8694.92</v>
+        <v>8667.4</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>93.94</v>
@@ -1130,10 +1130,10 @@
         <v>28</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>231153.11</v>
+        <v>216925.81</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>8255.469999999999</v>
+        <v>7747.35</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>7150.18</v>
@@ -1150,23 +1150,23 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
+          <t>AGENTE SOCIAL</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
         <v>25</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>127138.15</v>
+        <v>111377.89</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>5085.53</v>
+        <v>4455.12</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4449.86</v>
+        <v>4353.73</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>AGENTE SOCIAL</t>
+          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>115818.94</v>
+        <v>109636.8</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>4632.76</v>
+        <v>4568.2</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>4381.26</v>
+        <v>4422.34</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>76</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="15">
@@ -1211,13 +1211,13 @@
         <v>21</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>240266.19</v>
+        <v>268259.01</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>11441.25</v>
+        <v>12774.24</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>11926.93</v>
+        <v>12243.56</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>71.43000000000001</v>
@@ -1235,19 +1235,19 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>143806.39</v>
+        <v>114516.91</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>7190.32</v>
+        <v>6027.21</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>5076.59</v>
+        <v>5097.18</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>85</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1265,13 +1265,13 @@
         <v>16</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>194703.3</v>
+        <v>182709.56</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>12168.96</v>
+        <v>11419.35</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>12179.77</v>
+        <v>12122.69</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>56.25</v>
@@ -1292,13 +1292,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>132756.72</v>
+        <v>120833.78</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>11063.06</v>
+        <v>10069.48</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>8469.530000000001</v>
+        <v>8949.85</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>0</v>
@@ -1319,16 +1319,16 @@
         <v>10</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>160170.12</v>
+        <v>154527.9</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>16017.01</v>
+        <v>15452.79</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>15480.31</v>
+        <v>15452.79</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2270</v>
+        <v>2746</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3036582.75</v>
+        <v>5784035.99</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1337.7</v>
+        <v>2106.35</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1416.64</v>
+        <v>2572.32</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>95.52</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="21">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>2102</v>
+        <v>2165</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>27996123.24</v>
+        <v>28482602.03</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>13318.8</v>
+        <v>13155.94</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>12648.2</v>
+        <v>12503.93</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>96.48</v>
+        <v>96.26000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1397,19 +1397,19 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1704</v>
+        <v>1700</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>8504264.5</v>
+        <v>8534115.73</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>4990.77</v>
+        <v>5020.07</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>4722.97</v>
+        <v>4778.01</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>92.68000000000001</v>
+        <v>92.67</v>
       </c>
     </row>
     <row r="23">
@@ -1424,19 +1424,19 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>3136152.65</v>
+        <v>3278371.58</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>5733.37</v>
+        <v>5812.72</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>4599.99</v>
+        <v>4876.53</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>96.68000000000001</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>270397.44</v>
+        <v>253761.68</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>1044.01</v>
+        <v>1015.05</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>89.92</v>
+        <v>89.16</v>
       </c>
     </row>
     <row r="25">
@@ -1478,19 +1478,19 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1058446.85</v>
+        <v>1062205.79</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>4355.75</v>
+        <v>4425.86</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>4183.54</v>
+        <v>4156.02</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>63.6</v>
+        <v>62.71</v>
       </c>
     </row>
     <row r="26">
@@ -1505,19 +1505,19 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>829711.36</v>
+        <v>834860.13</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>5568.53</v>
+        <v>5640.95</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>5240.32</v>
+        <v>5212.8</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>56.08</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="27">
@@ -1532,19 +1532,19 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>2726024.44</v>
+        <v>2786952.59</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>19471.6</v>
+        <v>18830.76</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>17583.48</v>
+        <v>16466.09</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>82.14</v>
+        <v>80.41</v>
       </c>
     </row>
     <row r="28">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1715491.34</v>
+        <v>1668147.36</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>14662.32</v>
+        <v>14136.84</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>13237.05</v>
+        <v>13250.81</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>92.23999999999999</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="29">
@@ -1589,13 +1589,13 @@
         <v>95</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>510297.02</v>
+        <v>511967.92</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>5371.55</v>
+        <v>5389.14</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>5171.92</v>
+        <v>5104.76</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>74.19</v>
@@ -1616,13 +1616,13 @@
         <v>44</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>305290.74</v>
+        <v>393945.72</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>6938.43</v>
+        <v>8953.309999999999</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5515.31</v>
+        <v>8061.57</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>61.36</v>
@@ -1643,13 +1643,13 @@
         <v>32</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>207031.51</v>
+        <v>267943.48</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>6469.73</v>
+        <v>8373.23</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>5152.11</v>
+        <v>7060.9</v>
       </c>
       <c r="G31" s="15" t="n">
         <v>61.29</v>
@@ -1670,13 +1670,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>658959.6</v>
+        <v>702687.53</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>24405.91</v>
+        <v>26025.46</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>23288.88</v>
+        <v>26458.01</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>29.63</v>
@@ -1697,13 +1697,13 @@
         <v>22</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>262468.52</v>
+        <v>324197.66</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>11930.39</v>
+        <v>14736.26</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>11693.1</v>
+        <v>14448.13</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>81.81999999999999</v>
@@ -1724,13 +1724,13 @@
         <v>8</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>200144.1</v>
+        <v>160200.76</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>25018.01</v>
+        <v>20025.1</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>18607.9</v>
+        <v>18027.06</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>66.67</v>
@@ -1751,13 +1751,13 @@
         <v>8</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>74814.25999999999</v>
+        <v>79788.86</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>9351.780000000001</v>
+        <v>9973.610000000001</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>8076.06</v>
+        <v>10586.34</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>75</v>
@@ -1778,13 +1778,13 @@
         <v>6</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>76462.98</v>
+        <v>106174.11</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>12743.83</v>
+        <v>17695.69</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>10715.07</v>
+        <v>18255.97</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>50</v>
@@ -1805,13 +1805,13 @@
         <v>7</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>35675.99</v>
+        <v>36173.41</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>5096.57</v>
+        <v>5167.63</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>4449.86</v>
+        <v>4422.34</v>
       </c>
       <c r="G37" s="15" t="n">
         <v>57.14</v>
@@ -1832,13 +1832,13 @@
         <v>5</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>58465.51</v>
+        <v>54543.64</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>11693.1</v>
+        <v>10908.73</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>11990.23</v>
+        <v>11780.05</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>80</v>
@@ -1859,13 +1859,13 @@
         <v>5</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>28332.81</v>
+        <v>23416.84</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>5666.56</v>
+        <v>4683.37</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>5288.71</v>
+        <v>5033.9</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>60</v>
@@ -1886,10 +1886,10 @@
         <v>5</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>57030.69</v>
+        <v>63694.57</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>11406.14</v>
+        <v>12738.91</v>
       </c>
       <c r="F40" s="10" t="n">
         <v>11819.25</v>
@@ -1910,19 +1910,19 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>5098363.6</v>
+        <v>5089033.78</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>7771.9</v>
+        <v>7793.31</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>7270.99</v>
+        <v>7339.08</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>79.12</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="42">
@@ -1937,19 +1937,19 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>6528982.78</v>
+        <v>6224619.29</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>23070.61</v>
+        <v>22230.78</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>19003.68</v>
+        <v>18743.08</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>46.4</v>
+        <v>46.55</v>
       </c>
     </row>
     <row r="43">
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>4436821.89</v>
+        <v>4354202.38</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>16617.31</v>
+        <v>16186.63</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>14909.34</v>
+        <v>13833.87</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>89.43000000000001</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="44">
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1035997.79</v>
+        <v>1058113.18</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>4886.78</v>
+        <v>4898.67</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>4520.63</v>
+        <v>4552.07</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>61.9</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="45">
@@ -2018,19 +2018,19 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>716563.3199999999</v>
+        <v>770617.35</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>4874.58</v>
+        <v>5137.45</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>5194.79</v>
+        <v>5167.27</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>90.34</v>
+        <v>90.54000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2045,19 +2045,19 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>778343.0699999999</v>
+        <v>797851.0600000001</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>5442.96</v>
+        <v>5618.67</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>5132.77</v>
+        <v>5172.43</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>78.31999999999999</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="47">
@@ -2072,19 +2072,19 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>1827141.51</v>
+        <v>2072179.32</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>15100.34</v>
+        <v>17268.16</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>13353.68</v>
+        <v>14036.94</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>63.33</v>
+        <v>63.03</v>
       </c>
     </row>
     <row r="48">
@@ -2099,19 +2099,19 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>834366.04</v>
+        <v>800325.91</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>6953.05</v>
+        <v>6782.42</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6541.36</v>
+        <v>6477.78</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>5.88</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="49">
@@ -2129,16 +2129,16 @@
         <v>80</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>1683880.95</v>
+        <v>1718762.5</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>21048.51</v>
+        <v>21484.53</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>20431.36</v>
+        <v>20428.96</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>49.37</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="50">
@@ -2156,13 +2156,13 @@
         <v>80</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>565116.5600000001</v>
+        <v>526525.9300000001</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>7063.96</v>
+        <v>6581.57</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>6334.4</v>
+        <v>6136.61</v>
       </c>
       <c r="G50" s="11" t="n">
         <v>97.47</v>
@@ -2183,13 +2183,13 @@
         <v>23</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>171239.84</v>
+        <v>198055.06</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>7445.21</v>
+        <v>8611.09</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>5893.33</v>
+        <v>6189.21</v>
       </c>
       <c r="G51" s="15" t="n">
         <v>65.22</v>
@@ -2210,13 +2210,13 @@
         <v>21</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>151281.23</v>
+        <v>138064.94</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>7203.87</v>
+        <v>6574.52</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>5096.66</v>
+        <v>5402.54</v>
       </c>
       <c r="G52" s="11" t="n">
         <v>40</v>
@@ -2237,13 +2237,13 @@
         <v>19</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>210162.91</v>
+        <v>261641.84</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>11061.21</v>
+        <v>13770.62</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>12009.05</v>
+        <v>12121.47</v>
       </c>
       <c r="G53" s="15" t="n">
         <v>57.89</v>
@@ -2261,19 +2261,19 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>63196.21</v>
+        <v>68334.17</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>4861.25</v>
+        <v>5694.51</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>4974.31</v>
+        <v>4781.42</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="55">
@@ -2291,13 +2291,13 @@
         <v>12</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>203692.24</v>
+        <v>138454.46</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>16974.35</v>
+        <v>11537.87</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>10622.92</v>
+        <v>10358.74</v>
       </c>
       <c r="G55" s="15" t="n">
         <v>81.81999999999999</v>
@@ -2318,13 +2318,13 @@
         <v>8</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>135361.54</v>
+        <v>150827.62</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>16920.19</v>
+        <v>18853.45</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>15860.62</v>
+        <v>16064.49</v>
       </c>
       <c r="G56" s="11" t="n">
         <v>87.5</v>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>8604.48</v>
+        <v>7897.92</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>1075.56</v>
+        <v>1128.27</v>
       </c>
       <c r="F57" s="14" t="n">
         <v>1084.8</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>37.5</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="58">
@@ -2399,13 +2399,13 @@
         <v>5</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>45746.53</v>
+        <v>51591.36</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>9149.309999999999</v>
+        <v>10318.27</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>8590.99</v>
+        <v>9937.200000000001</v>
       </c>
       <c r="G59" s="15" t="n">
         <v>0</v>
@@ -2426,13 +2426,13 @@
         <v>5</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>45324.58</v>
+        <v>49583.61</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>9064.92</v>
+        <v>9916.719999999999</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>7131.74</v>
+        <v>8334.77</v>
       </c>
       <c r="G60" s="11" t="n">
         <v>40</v>
@@ -2453,13 +2453,13 @@
         <v>29</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>1035377.83</v>
+        <v>1010379.41</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>35702.68</v>
+        <v>34840.67</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>34944.5</v>
+        <v>35175.58</v>
       </c>
       <c r="G61" s="15" t="n">
         <v>48.28</v>
@@ -2477,19 +2477,19 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>160423.14</v>
+        <v>177963.78</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>5941.6</v>
+        <v>6844.76</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4638.59</v>
+        <v>5665.73</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -2500,23 +2500,23 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>AUX. DE ADMINISTRACAO</t>
+          <t>ESTAGIARIO NIVEL SUPERIOR</t>
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>94246.71000000001</v>
+        <v>19764.88</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>5890.42</v>
+        <v>1040.26</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5525.92</v>
+        <v>904.8</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>68.75</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="64">
@@ -2527,23 +2527,23 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>ESTAGIARIO NIVEL SUPERIOR</t>
+          <t>AUX. DE ADMINISTRACAO</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>16942.8</v>
+        <v>142615.84</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>1129.52</v>
+        <v>8389.17</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1084.8</v>
+        <v>8010.13</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>46.67</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="65">
@@ -2561,13 +2561,13 @@
         <v>12</v>
       </c>
       <c r="D65" s="14" t="n">
-        <v>139061.71</v>
+        <v>148016.93</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>11588.48</v>
+        <v>12334.74</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>11881.96</v>
+        <v>11822.88</v>
       </c>
       <c r="G65" s="15" t="n">
         <v>66.67</v>
@@ -2588,13 +2588,13 @@
         <v>9</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>139603.61</v>
+        <v>147283.01</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>15511.51</v>
+        <v>16364.78</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>15671.96</v>
+        <v>15781.88</v>
       </c>
       <c r="G66" s="11" t="n">
         <v>77.78</v>
@@ -2615,13 +2615,13 @@
         <v>5</v>
       </c>
       <c r="D67" s="14" t="n">
-        <v>312356.57</v>
+        <v>300696.51</v>
       </c>
       <c r="E67" s="14" t="n">
-        <v>62471.31</v>
+        <v>60139.3</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>56346.75</v>
+        <v>49803.64</v>
       </c>
       <c r="G67" s="15" t="n">
         <v>20</v>
@@ -2642,13 +2642,13 @@
         <v>7</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>81557.53999999999</v>
+        <v>94047.62</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>11651.08</v>
+        <v>13435.37</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>12261.82</v>
+        <v>12311.61</v>
       </c>
       <c r="G68" s="11" t="n">
         <v>85.70999999999999</v>
@@ -2666,19 +2666,19 @@
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" s="14" t="n">
-        <v>99341</v>
+        <v>84380.99000000001</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>14191.57</v>
+        <v>14063.5</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>15480.31</v>
+        <v>15452.79</v>
       </c>
       <c r="G69" s="15" t="n">
-        <v>28.57</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="70">
@@ -2696,10 +2696,10 @@
         <v>5</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>5362.4</v>
+        <v>5393.2</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>1072.48</v>
+        <v>1078.64</v>
       </c>
       <c r="F70" s="10" t="n">
         <v>1084.8</v>
@@ -2720,19 +2720,19 @@
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D71" s="14" t="n">
-        <v>19748.72</v>
+        <v>19526.4</v>
       </c>
       <c r="E71" s="14" t="n">
-        <v>1039.41</v>
+        <v>1084.8</v>
       </c>
       <c r="F71" s="14" t="n">
         <v>1084.8</v>
       </c>
       <c r="G71" s="15" t="n">
-        <v>47.37</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="72">
@@ -2750,13 +2750,13 @@
         <v>9</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>45083.73</v>
+        <v>56869.98</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>5009.3</v>
+        <v>6318.89</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>4819.73</v>
+        <v>5004.9</v>
       </c>
       <c r="G72" s="11" t="n">
         <v>55.56</v>
@@ -2777,13 +2777,13 @@
         <v>9</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>57356.97</v>
+        <v>52422.31</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>6373</v>
+        <v>5824.7</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>4827.3</v>
+        <v>4752.6</v>
       </c>
       <c r="G73" s="15" t="n">
         <v>33.33</v>
@@ -2804,13 +2804,13 @@
         <v>5</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>33684.37</v>
+        <v>32880.04</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>6736.87</v>
+        <v>6576.01</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>5116.99</v>
+        <v>5089.47</v>
       </c>
       <c r="G74" s="11" t="n">
         <v>60</v>
@@ -2831,13 +2831,13 @@
         <v>5</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>32676.65</v>
+        <v>36638.48</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>6535.33</v>
+        <v>7327.7</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>4575.66</v>
+        <v>5228.05</v>
       </c>
       <c r="G75" s="15" t="n">
         <v>100</v>
@@ -2858,13 +2858,13 @@
         <v>5</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>51670.7</v>
+        <v>51935.93</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>10334.14</v>
+        <v>10387.19</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>11624.91</v>
+        <v>11459.79</v>
       </c>
       <c r="G76" s="11" t="n">
         <v>80</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D77" s="14" t="n">
-        <v>315651.19</v>
+        <v>307538.06</v>
       </c>
       <c r="E77" s="14" t="n">
-        <v>10884.52</v>
+        <v>10983.5</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>7692.79</v>
+        <v>8902.379999999999</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>17.86</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="78">
@@ -2912,13 +2912,13 @@
         <v>10</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>54960.32</v>
+        <v>58715.8</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>5496.03</v>
+        <v>5871.58</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>5057.98</v>
+        <v>5307.64</v>
       </c>
       <c r="G78" s="11" t="n">
         <v>50</v>
@@ -2939,13 +2939,13 @@
         <v>10</v>
       </c>
       <c r="D79" s="14" t="n">
-        <v>92317.27</v>
+        <v>92516.61</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>9231.73</v>
+        <v>9251.66</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>7795.98</v>
+        <v>7638.65</v>
       </c>
       <c r="G79" s="15" t="n">
         <v>20</v>
@@ -2963,19 +2963,19 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>88850.81</v>
+        <v>85538.48</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>12692.97</v>
+        <v>10692.31</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>15480.31</v>
+        <v>12192.33</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="81">
@@ -2993,10 +2993,10 @@
         <v>7</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>8184.24</v>
+        <v>8164.16</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>1169.18</v>
+        <v>1166.31</v>
       </c>
       <c r="F81" s="14" t="n">
         <v>1084.8</v>
@@ -3020,13 +3020,13 @@
         <v>6</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>66787.81</v>
+        <v>65728.24000000001</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>11131.3</v>
+        <v>10954.71</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>10790.44</v>
+        <v>10410.07</v>
       </c>
       <c r="G82" s="11" t="n">
         <v>33.33</v>
@@ -3047,13 +3047,13 @@
         <v>5</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>27104.41</v>
+        <v>21483.79</v>
       </c>
       <c r="E83" s="14" t="n">
-        <v>5420.88</v>
+        <v>4296.76</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>5205.63</v>
+        <v>3725.13</v>
       </c>
       <c r="G83" s="15" t="n">
         <v>40</v>
@@ -3071,19 +3071,19 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>29590.64</v>
+        <v>35883.6</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>1056.81</v>
+        <v>1025.25</v>
       </c>
       <c r="F84" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>46.43</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="85">
@@ -3101,10 +3101,10 @@
         <v>25</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>308078.83</v>
+        <v>334184.41</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>12323.15</v>
+        <v>13367.38</v>
       </c>
       <c r="F85" s="14" t="n">
         <v>9902.75</v>
@@ -3128,13 +3128,13 @@
         <v>13</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>66077.10000000001</v>
+        <v>63839.47</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>5082.85</v>
+        <v>4910.73</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>4594.22</v>
+        <v>4484.15</v>
       </c>
       <c r="G86" s="11" t="n">
         <v>84.62</v>
@@ -3155,13 +3155,13 @@
         <v>12</v>
       </c>
       <c r="D87" s="14" t="n">
-        <v>66492.50999999999</v>
+        <v>65138.38</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>5541.04</v>
+        <v>5428.2</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>5178.73</v>
+        <v>5004.45</v>
       </c>
       <c r="G87" s="15" t="n">
         <v>41.67</v>
@@ -3182,13 +3182,13 @@
         <v>10</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>116111.47</v>
+        <v>123556.55</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>11611.15</v>
+        <v>12355.66</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>12349.83</v>
+        <v>12380.56</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>50</v>
@@ -3209,13 +3209,13 @@
         <v>9</v>
       </c>
       <c r="D89" s="14" t="n">
-        <v>88088.5</v>
+        <v>93678.82000000001</v>
       </c>
       <c r="E89" s="14" t="n">
-        <v>9787.610000000001</v>
+        <v>10408.76</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>7727.56</v>
+        <v>10188.61</v>
       </c>
       <c r="G89" s="15" t="n">
         <v>55.56</v>
@@ -3236,13 +3236,13 @@
         <v>9</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>55609.54</v>
+        <v>50014.84</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>6178.84</v>
+        <v>5557.2</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>6016.47</v>
+        <v>5730.23</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>11.11</v>
@@ -3256,23 +3256,23 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>CHEFE DE DIVISAO</t>
+          <t>ASSESSOR DE GABINETE</t>
         </is>
       </c>
       <c r="C91" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D91" s="14" t="n">
-        <v>119273.45</v>
+        <v>137007.92</v>
       </c>
       <c r="E91" s="14" t="n">
-        <v>14909.18</v>
+        <v>15223.1</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>15830.08</v>
+        <v>15452.79</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>37.5</v>
+        <v>55.56</v>
       </c>
     </row>
     <row r="92">
@@ -3283,23 +3283,23 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ASSESSOR DE GABINETE</t>
+          <t>CHEFE DE DIVISAO</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>92719.24000000001</v>
+        <v>163055.87</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>13245.61</v>
+        <v>20381.98</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>15480.31</v>
+        <v>16390.17</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>71.43000000000001</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="93">
@@ -3317,13 +3317,13 @@
         <v>5</v>
       </c>
       <c r="D93" s="14" t="n">
-        <v>114293.83</v>
+        <v>115671.82</v>
       </c>
       <c r="E93" s="14" t="n">
-        <v>22858.77</v>
+        <v>23134.36</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>15079.43</v>
+        <v>16261.14</v>
       </c>
       <c r="G93" s="15" t="n">
         <v>80</v>
@@ -3341,19 +3341,19 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>311089.46</v>
+        <v>308893.76</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>14813.78</v>
+        <v>15444.69</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>15480.31</v>
+        <v>15452.79</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>42.86</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95">
@@ -3371,16 +3371,16 @@
         <v>18</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>18484.48</v>
+        <v>17347.44</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>1026.92</v>
+        <v>963.75</v>
       </c>
       <c r="F95" s="14" t="n">
         <v>1084.8</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>64.70999999999999</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="96">
@@ -3395,16 +3395,16 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>84906.08</v>
+        <v>81559.38</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>5306.63</v>
+        <v>5437.29</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>4991.68</v>
+        <v>4667.43</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>60</v>
@@ -3425,16 +3425,16 @@
         <v>11</v>
       </c>
       <c r="D97" s="14" t="n">
-        <v>149626.29</v>
+        <v>179951.06</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>13602.39</v>
+        <v>16359.19</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>12271.09</v>
+        <v>13527.88</v>
       </c>
       <c r="G97" s="15" t="n">
-        <v>72.73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98">
@@ -3452,13 +3452,13 @@
         <v>8</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>132547.27</v>
+        <v>161828.18</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>16568.41</v>
+        <v>20228.52</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>15945.58</v>
+        <v>15620.79</v>
       </c>
       <c r="G98" s="11" t="n">
         <v>50</v>
@@ -3476,19 +3476,19 @@
         </is>
       </c>
       <c r="C99" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>78034.03</v>
+        <v>99124.94</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>13005.67</v>
+        <v>14160.71</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>11143.89</v>
+        <v>14087.82</v>
       </c>
       <c r="G99" s="15" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -3506,13 +3506,13 @@
         <v>6</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>86449.66</v>
+        <v>82846.00999999999</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>14408.28</v>
+        <v>13807.67</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>14935.56</v>
+        <v>14675.78</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>66.67</v>
@@ -3533,13 +3533,13 @@
         <v>5</v>
       </c>
       <c r="D101" s="14" t="n">
-        <v>46592.04</v>
+        <v>43184.37</v>
       </c>
       <c r="E101" s="14" t="n">
-        <v>9318.41</v>
+        <v>8636.870000000001</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>6872.75</v>
+        <v>6423.31</v>
       </c>
       <c r="G101" s="15" t="n">
         <v>0</v>
@@ -3560,13 +3560,13 @@
         <v>13</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>60377.17</v>
+        <v>56224.95</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>4644.4</v>
+        <v>4325</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>4449.86</v>
+        <v>4422.34</v>
       </c>
       <c r="G102" s="11" t="n">
         <v>38.46</v>
@@ -3584,19 +3584,19 @@
         </is>
       </c>
       <c r="C103" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D103" s="14" t="n">
-        <v>9732.4</v>
+        <v>8892.719999999999</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>1081.38</v>
+        <v>889.27</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>1084.8</v>
+        <v>1069.4</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="104">
@@ -3607,23 +3607,23 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ENG.CIVIL I</t>
+          <t>CHEFE DE SECAO</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>91959.47</v>
+        <v>71318.06</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>13137.07</v>
+        <v>11886.34</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>12085.13</v>
+        <v>12116.39</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>14.29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105">
@@ -3634,23 +3634,23 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>CHEFE DE SECAO</t>
+          <t>ENG.CIVIL I</t>
         </is>
       </c>
       <c r="C105" s="13" t="n">
         <v>6</v>
       </c>
       <c r="D105" s="14" t="n">
-        <v>66612.78</v>
+        <v>82895.98</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>11102.13</v>
+        <v>13816</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>12201.86</v>
+        <v>13327</v>
       </c>
       <c r="G105" s="15" t="n">
-        <v>50</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="106">
@@ -3668,13 +3668,13 @@
         <v>6</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>33461.72</v>
+        <v>36043.81</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>5576.95</v>
+        <v>6007.3</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>5335.12</v>
+        <v>5363.28</v>
       </c>
       <c r="G106" s="11" t="n">
         <v>0</v>
@@ -3695,13 +3695,13 @@
         <v>5</v>
       </c>
       <c r="D107" s="14" t="n">
-        <v>22941.46</v>
+        <v>24281.66</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>4588.29</v>
+        <v>4856.33</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>4167.35</v>
+        <v>4482.18</v>
       </c>
       <c r="G107" s="15" t="n">
         <v>0</v>
@@ -3719,19 +3719,19 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>126763.16</v>
+        <v>112361.94</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>11523.92</v>
+        <v>11236.19</v>
       </c>
       <c r="F108" s="10" t="n">
         <v>9457.52</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>36.36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109">
@@ -3749,10 +3749,10 @@
         <v>9</v>
       </c>
       <c r="D109" s="14" t="n">
-        <v>9664.639999999999</v>
+        <v>9068.4</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>1073.85</v>
+        <v>1007.6</v>
       </c>
       <c r="F109" s="14" t="n">
         <v>1084.8</v>
@@ -3776,13 +3776,13 @@
         <v>6</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>80318.67999999999</v>
+        <v>80013.28</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>13386.45</v>
+        <v>13335.55</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>11314.94</v>
+        <v>11388.65</v>
       </c>
       <c r="G110" s="11" t="n">
         <v>83.33</v>
@@ -3800,19 +3800,19 @@
         </is>
       </c>
       <c r="C111" s="13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D111" s="14" t="n">
-        <v>305633</v>
+        <v>311892.73</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>7276.98</v>
+        <v>7088.47</v>
       </c>
       <c r="F111" s="14" t="n">
-        <v>7103.34</v>
+        <v>6982.16</v>
       </c>
       <c r="G111" s="15" t="n">
-        <v>21.43</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="112">
@@ -3827,19 +3827,19 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>28412.72</v>
+        <v>24845.44</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>1092.8</v>
+        <v>1035.23</v>
       </c>
       <c r="F112" s="10" t="n">
         <v>1084.8</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>80.77</v>
+        <v>79.17</v>
       </c>
     </row>
     <row r="113">
@@ -3857,13 +3857,13 @@
         <v>22</v>
       </c>
       <c r="D113" s="14" t="n">
-        <v>224719.88</v>
+        <v>281110.59</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>10214.54</v>
+        <v>12777.75</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>7566.69</v>
+        <v>7915.79</v>
       </c>
       <c r="G113" s="15" t="n">
         <v>45.45</v>
@@ -3884,13 +3884,13 @@
         <v>20</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>275684.33</v>
+        <v>282480.89</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>13784.22</v>
+        <v>14124.04</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>11452.56</v>
+        <v>11938.45</v>
       </c>
       <c r="G114" s="11" t="n">
         <v>25</v>
@@ -3911,13 +3911,13 @@
         <v>16</v>
       </c>
       <c r="D115" s="14" t="n">
-        <v>203390.58</v>
+        <v>205058.27</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>12711.91</v>
+        <v>12816.14</v>
       </c>
       <c r="F115" s="14" t="n">
-        <v>11997.73</v>
+        <v>12033.12</v>
       </c>
       <c r="G115" s="15" t="n">
         <v>62.5</v>
@@ -3931,23 +3931,23 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
+          <t>AUX. DE ADMINISTRACAO</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>79027.24000000001</v>
+        <v>75852.00999999999</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>6079.02</v>
+        <v>6321</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>4449.86</v>
+        <v>5672.16</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>53.85</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -3958,23 +3958,23 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>AUX. DE ADMINISTRACAO</t>
+          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C117" s="13" t="n">
         <v>12</v>
       </c>
       <c r="D117" s="14" t="n">
-        <v>75850.74000000001</v>
+        <v>76713.53</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>6320.9</v>
+        <v>6392.79</v>
       </c>
       <c r="F117" s="14" t="n">
-        <v>5751.57</v>
+        <v>4548.16</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>81.81999999999999</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="118">
@@ -3992,13 +3992,13 @@
         <v>8</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>128414.2</v>
+        <v>126797.16</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>16051.78</v>
+        <v>15849.65</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>13760.33</v>
+        <v>13868.72</v>
       </c>
       <c r="G118" s="11" t="n">
         <v>62.5</v>
@@ -4019,13 +4019,13 @@
         <v>6</v>
       </c>
       <c r="D119" s="14" t="n">
-        <v>92189.5</v>
+        <v>92101.2</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>15364.92</v>
+        <v>15350.2</v>
       </c>
       <c r="F119" s="14" t="n">
-        <v>15646.63</v>
+        <v>15231.39</v>
       </c>
       <c r="G119" s="15" t="n">
         <v>50</v>
@@ -4043,19 +4043,19 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>303086.81</v>
+        <v>279054.48</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>7392.36</v>
+        <v>6976.36</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5769.6</v>
+        <v>6039.33</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>60.53</v>
+        <v>59.46</v>
       </c>
     </row>
     <row r="121">
@@ -4073,13 +4073,13 @@
         <v>22</v>
       </c>
       <c r="D121" s="14" t="n">
-        <v>187774.5</v>
+        <v>185364.84</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>8535.200000000001</v>
+        <v>8425.67</v>
       </c>
       <c r="F121" s="14" t="n">
-        <v>6739.08</v>
+        <v>6817.83</v>
       </c>
       <c r="G121" s="15" t="n">
         <v>90.91</v>
@@ -4097,19 +4097,19 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>173558.36</v>
+        <v>234546.24</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>12397.03</v>
+        <v>15636.42</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>12288.73</v>
+        <v>13123.52</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123">
@@ -4127,10 +4127,10 @@
         <v>8</v>
       </c>
       <c r="D123" s="14" t="n">
-        <v>8610.639999999999</v>
+        <v>8172.72</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>1076.33</v>
+        <v>1021.59</v>
       </c>
       <c r="F123" s="14" t="n">
         <v>1084.8</v>
@@ -4154,13 +4154,13 @@
         <v>6</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>98576.00999999999</v>
+        <v>99407.99000000001</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>16429.33</v>
+        <v>16568</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>16502.95</v>
+        <v>17200.97</v>
       </c>
       <c r="G124" s="11" t="n">
         <v>66.67</v>
@@ -4181,13 +4181,13 @@
         <v>6</v>
       </c>
       <c r="D125" s="14" t="n">
-        <v>34958.76</v>
+        <v>32388.81</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>5826.46</v>
+        <v>5398.14</v>
       </c>
       <c r="F125" s="14" t="n">
-        <v>5241.5</v>
+        <v>5212.8</v>
       </c>
       <c r="G125" s="15" t="n">
         <v>50</v>
@@ -4208,13 +4208,13 @@
         <v>5</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>76566.85000000001</v>
+        <v>59603.11</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>15313.37</v>
+        <v>11920.62</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>12524.34</v>
+        <v>12342.47</v>
       </c>
       <c r="G126" s="11" t="n">
         <v>100</v>
@@ -4232,19 +4232,19 @@
         </is>
       </c>
       <c r="C127" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D127" s="14" t="n">
-        <v>56816.3</v>
+        <v>61399.71</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>8116.61</v>
+        <v>7674.96</v>
       </c>
       <c r="F127" s="14" t="n">
-        <v>5089</v>
+        <v>5351.85</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="128">
@@ -4255,50 +4255,50 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>ESTAGIARIO NIVEL SUPERIOR</t>
+          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>6994</v>
+        <v>22525.94</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>999.14</v>
+        <v>3754.32</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>1084.8</v>
+        <v>4241.5</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
+          <t>GCM-2A CLASSE</t>
         </is>
       </c>
       <c r="C129" s="13" t="n">
-        <v>6</v>
+        <v>336</v>
       </c>
       <c r="D129" s="14" t="n">
-        <v>29292.94</v>
+        <v>2533852.28</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>4882.16</v>
+        <v>7541.23</v>
       </c>
       <c r="F129" s="14" t="n">
-        <v>4544.22</v>
+        <v>6526.29</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>66.67</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="130">
@@ -4309,23 +4309,23 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>GCM-2A CLASSE</t>
+          <t>GCM-1A CLASSE</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>340</v>
+        <v>111</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>2579600.95</v>
+        <v>1618155.77</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>7587.06</v>
+        <v>14577.98</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>6553.81</v>
+        <v>13905.64</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>19.53</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="131">
@@ -4336,23 +4336,23 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>GCM-1A CLASSE</t>
+          <t>GCM-CLASSE ESPECIAL</t>
         </is>
       </c>
       <c r="C131" s="13" t="n">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="D131" s="14" t="n">
-        <v>1549193.56</v>
+        <v>586487.83</v>
       </c>
       <c r="E131" s="14" t="n">
-        <v>13832.09</v>
+        <v>14662.2</v>
       </c>
       <c r="F131" s="14" t="n">
-        <v>13555.06</v>
+        <v>14524.74</v>
       </c>
       <c r="G131" s="15" t="n">
-        <v>9.01</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="132">
@@ -4363,23 +4363,23 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>GCM-CLASSE ESPECIAL</t>
+          <t>ESTAGIARIO NIVEL SUPERIOR</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>581085.99</v>
+        <v>26813.6</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>14527.15</v>
+        <v>1072.54</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>14711.15</v>
+        <v>1084.8</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>17.95</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="133">
@@ -4390,23 +4390,23 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>ESTAGIARIO NIVEL SUPERIOR</t>
+          <t>GCM-CLASSE DISTINTA</t>
         </is>
       </c>
       <c r="C133" s="13" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D133" s="14" t="n">
-        <v>27345.04</v>
+        <v>404695.15</v>
       </c>
       <c r="E133" s="14" t="n">
-        <v>1051.73</v>
+        <v>20234.76</v>
       </c>
       <c r="F133" s="14" t="n">
-        <v>1084.8</v>
+        <v>18033.22</v>
       </c>
       <c r="G133" s="15" t="n">
-        <v>92</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134">
@@ -4417,23 +4417,23 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>GCM-CLASSE DISTINTA</t>
+          <t>AUX. DE SERVICOS OPERACIONAIS</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>388293.15</v>
+        <v>59741.39</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>19414.66</v>
+        <v>7467.67</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>18561.26</v>
+        <v>7316.97</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4444,23 +4444,23 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>AUX. DE SERVICOS OPERACIONAIS</t>
+          <t>CHEFE DE SECAO</t>
         </is>
       </c>
       <c r="C135" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D135" s="14" t="n">
-        <v>60264.05</v>
+        <v>95468.71000000001</v>
       </c>
       <c r="E135" s="14" t="n">
-        <v>7533.01</v>
+        <v>13638.39</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>7347.41</v>
+        <v>12549.88</v>
       </c>
       <c r="G135" s="15" t="n">
-        <v>0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="136">
@@ -4471,47 +4471,47 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>CHEFE DE SECAO</t>
+          <t>AUX. DE ADMINISTRACAO</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>92635.05</v>
+        <v>40178.08</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>13233.58</v>
+        <v>8035.62</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>14634.9</v>
+        <v>5951.03</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>28.57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>AUX. DE ADMINISTRACAO</t>
+          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C137" s="13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D137" s="14" t="n">
-        <v>42162.97</v>
+        <v>86597.08</v>
       </c>
       <c r="E137" s="14" t="n">
-        <v>8432.59</v>
+        <v>4329.85</v>
       </c>
       <c r="F137" s="14" t="n">
-        <v>6103.97</v>
+        <v>4422.34</v>
       </c>
       <c r="G137" s="15" t="n">
         <v>60</v>
@@ -4525,23 +4525,23 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
+          <t>CHEFE DE SECAO</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>89468.23</v>
+        <v>159598.73</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>4473.41</v>
+        <v>12276.83</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>4449.86</v>
+        <v>11756.15</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>60</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="139">
@@ -4552,20 +4552,20 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>CHEFE DE SECAO</t>
+          <t>AGENTE DE SERVICO CEMITERIAL</t>
         </is>
       </c>
       <c r="C139" s="13" t="n">
         <v>13</v>
       </c>
       <c r="D139" s="14" t="n">
-        <v>165520.98</v>
+        <v>68478.77</v>
       </c>
       <c r="E139" s="14" t="n">
-        <v>12732.38</v>
+        <v>5267.6</v>
       </c>
       <c r="F139" s="14" t="n">
-        <v>12217.58</v>
+        <v>4883.2</v>
       </c>
       <c r="G139" s="15" t="n">
         <v>30.77</v>
@@ -4579,23 +4579,23 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>AGENTE DE SERVICO CEMITERIAL</t>
+          <t>ELETRICISTA</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>72578.25999999999</v>
+        <v>72733.23</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>5582.94</v>
+        <v>6061.1</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>5461.11</v>
+        <v>5945.74</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -4606,23 +4606,23 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>ELETRICISTA</t>
+          <t>ENG.CIVIL I</t>
         </is>
       </c>
       <c r="C141" s="13" t="n">
         <v>12</v>
       </c>
       <c r="D141" s="14" t="n">
-        <v>70820.64</v>
+        <v>163638.41</v>
       </c>
       <c r="E141" s="14" t="n">
-        <v>5901.72</v>
+        <v>13636.53</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>5664.05</v>
+        <v>10358.14</v>
       </c>
       <c r="G141" s="15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="142">
@@ -4633,23 +4633,23 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>ENG.CIVIL I</t>
+          <t>ASSESSOR DE GABINETE</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
         <v>12</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>133254.14</v>
+        <v>163769.56</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>11104.51</v>
+        <v>13647.46</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>10396.1</v>
+        <v>15452.79</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>50</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="143">
@@ -4660,23 +4660,23 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>ASSESSOR DE GABINETE</t>
+          <t>AJUDANTE GERAL</t>
         </is>
       </c>
       <c r="C143" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D143" s="14" t="n">
-        <v>153322.15</v>
+        <v>52762.63</v>
       </c>
       <c r="E143" s="14" t="n">
-        <v>15332.22</v>
+        <v>5862.51</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>15480.31</v>
+        <v>5457.28</v>
       </c>
       <c r="G143" s="15" t="n">
-        <v>10</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="144">
@@ -4687,23 +4687,23 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>AJUDANTE GERAL</t>
+          <t>AUX. DE ADMINISTRACAO</t>
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>45486.51</v>
+        <v>48220.48</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>5054.06</v>
+        <v>8036.75</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>4431.21</v>
+        <v>8219.92</v>
       </c>
       <c r="G144" s="11" t="n">
-        <v>22.22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="145">
@@ -4714,23 +4714,23 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>AUX. DE ADMINISTRACAO</t>
+          <t>PEDREIRO</t>
         </is>
       </c>
       <c r="C145" s="13" t="n">
         <v>6</v>
       </c>
       <c r="D145" s="14" t="n">
-        <v>47348.38</v>
+        <v>22868.72</v>
       </c>
       <c r="E145" s="14" t="n">
-        <v>7891.4</v>
+        <v>3811.45</v>
       </c>
       <c r="F145" s="14" t="n">
-        <v>7999.02</v>
+        <v>3807.8</v>
       </c>
       <c r="G145" s="15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -4748,13 +4748,13 @@
         <v>5</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>79531.86</v>
+        <v>81160.87</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>15906.37</v>
+        <v>16232.17</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>16052.54</v>
+        <v>15722.3</v>
       </c>
       <c r="G146" s="11" t="n">
         <v>100</v>
@@ -4763,28 +4763,28 @@
     <row r="147">
       <c r="A147" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>ENG.ELETRICISTA I</t>
+          <t>CHEFE DE SECAO</t>
         </is>
       </c>
       <c r="C147" s="13" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D147" s="14" t="n">
-        <v>62659.41</v>
+        <v>197312.48</v>
       </c>
       <c r="E147" s="14" t="n">
-        <v>12531.88</v>
+        <v>11606.62</v>
       </c>
       <c r="F147" s="14" t="n">
-        <v>13225.14</v>
+        <v>11979.29</v>
       </c>
       <c r="G147" s="15" t="n">
-        <v>0</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="148">
@@ -4795,23 +4795,23 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>CHEFE DE SECAO</t>
+          <t>ESTAGIARIO NIVEL SUPERIOR</t>
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>204346.83</v>
+        <v>14952.32</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>12020.4</v>
+        <v>996.8200000000001</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>11905.76</v>
+        <v>1084.8</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="149">
@@ -4822,23 +4822,23 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>ESTAGIARIO NIVEL SUPERIOR</t>
+          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="C149" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D149" s="14" t="n">
-        <v>15608</v>
+        <v>71653.74000000001</v>
       </c>
       <c r="E149" s="14" t="n">
-        <v>1114.86</v>
+        <v>5511.83</v>
       </c>
       <c r="F149" s="14" t="n">
-        <v>1084.8</v>
+        <v>4634.65</v>
       </c>
       <c r="G149" s="15" t="n">
-        <v>57.14</v>
+        <v>61.54</v>
       </c>
     </row>
     <row r="150">
@@ -4849,23 +4849,23 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
+          <t>TECNICO AMBIENTAL</t>
         </is>
       </c>
       <c r="C150" s="9" t="n">
         <v>13</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>67376.87</v>
+        <v>134614.27</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>5182.84</v>
+        <v>10354.94</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4449.86</v>
+        <v>9521.290000000001</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>61.54</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="151">
@@ -4876,23 +4876,23 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>TECNICO AMBIENTAL</t>
+          <t>AUX. DE ADMINISTRACAO</t>
         </is>
       </c>
       <c r="C151" s="13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D151" s="14" t="n">
-        <v>124790.27</v>
+        <v>100432.69</v>
       </c>
       <c r="E151" s="14" t="n">
-        <v>9599.25</v>
+        <v>9130.24</v>
       </c>
       <c r="F151" s="14" t="n">
-        <v>8873.9</v>
+        <v>6859.48</v>
       </c>
       <c r="G151" s="15" t="n">
-        <v>53.85</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="152">
@@ -4903,23 +4903,23 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>AUX. DE ADMINISTRACAO</t>
+          <t>AGENTE DE VIG.SANITARIA I</t>
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>93527.86</v>
+        <v>46221.86</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>8502.530000000001</v>
+        <v>5777.73</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>6055.7</v>
+        <v>5871.1</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>72.73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="153">
@@ -4930,20 +4930,20 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>AGENTE DE VIG.SANITARIA I</t>
+          <t>CHEFE DE DIVISAO</t>
         </is>
       </c>
       <c r="C153" s="13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D153" s="14" t="n">
-        <v>50416.56</v>
+        <v>95646.88</v>
       </c>
       <c r="E153" s="14" t="n">
-        <v>6302.07</v>
+        <v>15941.15</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>6241.51</v>
+        <v>15872.97</v>
       </c>
       <c r="G153" s="15" t="n">
         <v>50</v>
@@ -4957,54 +4957,27 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>CHEFE DE DIVISAO</t>
+          <t>MED VETERINARIO 150H</t>
         </is>
       </c>
       <c r="C154" s="9" t="n">
         <v>6</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>103663.14</v>
+        <v>80631.64999999999</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>17277.19</v>
+        <v>13438.61</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>15900.5</v>
+        <v>14317.54</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="12" t="inlineStr">
-        <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
-        </is>
-      </c>
-      <c r="B155" s="12" t="inlineStr">
-        <is>
-          <t>MED VETERINARIO 150H</t>
-        </is>
-      </c>
-      <c r="C155" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D155" s="14" t="n">
-        <v>78861.10000000001</v>
-      </c>
-      <c r="E155" s="14" t="n">
-        <v>13143.52</v>
-      </c>
-      <c r="F155" s="14" t="n">
-        <v>14317.55</v>
-      </c>
-      <c r="G155" s="15" t="n">
         <v>83.33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G155"/>
+  <autoFilter ref="A1:G154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>